--- a/exports/trend_1d/SONACOMS_full_report.xlsx
+++ b/exports/trend_1d/SONACOMS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>22.55</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H2" t="n">
-        <v>697.6</v>
+        <v>643.35</v>
       </c>
       <c r="I2" t="n">
         <v>646.4925230511983</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" t="n">
-        <v>73.34</v>
+        <v>59.86</v>
       </c>
       <c r="L2" t="n">
         <v>3.59</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>27.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="H3" t="n">
-        <v>741.85</v>
+        <v>759.95</v>
       </c>
       <c r="I3" t="n">
         <v>759.8018518134979</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.31</v>
+        <v>-18.12</v>
       </c>
       <c r="L3" t="n">
-        <v>19.59</v>
+        <v>20.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.27</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H4" t="n">
-        <v>755.85</v>
+        <v>699.25</v>
       </c>
       <c r="I4" t="n">
         <v>712.1889614913226</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.54</v>
+        <v>-7.99</v>
       </c>
       <c r="L4" t="n">
         <v>11.02</v>
@@ -669,7 +716,7 @@
         <v>1.97</v>
       </c>
       <c r="N4" t="n">
-        <v>4.03</v>
+        <v>7.49</v>
       </c>
       <c r="O4" t="n">
         <v>2.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>19.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H5" t="n">
-        <v>644.5</v>
+        <v>684.5</v>
       </c>
       <c r="I5" t="n">
         <v>667.0318852898124</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="n">
-        <v>7.83</v>
+        <v>2.11</v>
       </c>
       <c r="L5" t="n">
         <v>13.66</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>15.41</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H6" t="n">
-        <v>613.85</v>
+        <v>595.1</v>
       </c>
       <c r="I6" t="n">
         <v>607.2715117916388</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.32</v>
+        <v>-13.06</v>
       </c>
       <c r="L6" t="n">
-        <v>11.45</v>
+        <v>13.73</v>
       </c>
       <c r="M6" t="n">
         <v>1.42</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.91</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44908</v>
+        <v>44909</v>
       </c>
       <c r="H7" t="n">
-        <v>449.9</v>
+        <v>479.2</v>
       </c>
       <c r="I7" t="n">
         <v>469.3600354583045</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K7" t="n">
-        <v>24.4</v>
+        <v>19.48</v>
       </c>
       <c r="L7" t="n">
         <v>4.02</v>
@@ -840,7 +923,7 @@
         <v>2.37</v>
       </c>
       <c r="N7" t="n">
-        <v>5.93</v>
+        <v>6.51</v>
       </c>
       <c r="O7" t="n">
         <v>-3.05</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H8" t="n">
-        <v>435.9</v>
+        <v>423.15</v>
       </c>
       <c r="I8" t="n">
         <v>428.0188199160499</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.039999999999999</v>
+        <v>-11.7</v>
       </c>
       <c r="L8" t="n">
-        <v>9.82</v>
+        <v>12.08</v>
       </c>
       <c r="M8" t="n">
         <v>0.52</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.65</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="H9" t="n">
-        <v>432.6</v>
+        <v>455</v>
       </c>
       <c r="I9" t="n">
         <v>449.8304461610269</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.23</v>
+        <v>-7.53</v>
       </c>
       <c r="L9" t="n">
-        <v>8.42</v>
+        <v>8.94</v>
       </c>
       <c r="M9" t="n">
         <v>5.56</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>11.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44995</v>
+        <v>44998</v>
       </c>
       <c r="H10" t="n">
-        <v>436.3</v>
+        <v>406.2</v>
       </c>
       <c r="I10" t="n">
         <v>424.1441873547275</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.11</v>
+        <v>-10.73</v>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>11.36</v>
       </c>
       <c r="M10" t="n">
-        <v>0.85</v>
+        <v>5.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.84</v>
+        <v>6.9</v>
       </c>
       <c r="O10" t="n">
         <v>5.18</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>14.27</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H11" t="n">
-        <v>444.35</v>
+        <v>459.2</v>
       </c>
       <c r="I11" t="n">
         <v>451.0794699790368</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.390000000000001</v>
+        <v>-13.05</v>
       </c>
       <c r="L11" t="n">
-        <v>9.77</v>
+        <v>13.8</v>
       </c>
       <c r="M11" t="n">
         <v>2.29</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.98</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45139</v>
+        <v>45140</v>
       </c>
       <c r="H12" t="n">
-        <v>567.05</v>
+        <v>554.6</v>
       </c>
       <c r="I12" t="n">
         <v>556.4013900849553</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K12" t="n">
-        <v>23.49</v>
+        <v>20.78</v>
       </c>
       <c r="L12" t="n">
         <v>4.7</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45156</v>
+        <v>45159</v>
       </c>
       <c r="H13" t="n">
-        <v>566.85</v>
+        <v>590.9</v>
       </c>
       <c r="I13" t="n">
         <v>586.9786154860574</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.21</v>
+        <v>-6.55</v>
       </c>
       <c r="L13" t="n">
-        <v>3.95</v>
+        <v>7.27</v>
       </c>
       <c r="M13" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>2.24</v>
+        <v>4.24</v>
       </c>
       <c r="O13" t="n">
         <v>-2.2</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>9.18</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H14" t="n">
-        <v>569.1</v>
+        <v>555.1</v>
       </c>
       <c r="I14" t="n">
         <v>555.896683341638</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.69</v>
+        <v>-6.06</v>
       </c>
       <c r="L14" t="n">
-        <v>4.21</v>
+        <v>6.87</v>
       </c>
       <c r="M14" t="n">
         <v>0.99</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H15" t="n">
-        <v>548.45</v>
+        <v>556.15</v>
       </c>
       <c r="I15" t="n">
         <v>552.9705522342617</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2</v>
+        <v>-0.19</v>
       </c>
       <c r="L15" t="n">
         <v>2.43</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H16" t="n">
-        <v>560.35</v>
+        <v>538</v>
       </c>
       <c r="I16" t="n">
         <v>540.2869516352669</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K16" t="n">
-        <v>0.76</v>
+        <v>-3.26</v>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>3.94</v>
       </c>
       <c r="M16" t="n">
         <v>0.18</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>3.99</v>
       </c>
       <c r="O16" t="n">
         <v>1.4</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>10.87</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45286</v>
+        <v>45287</v>
       </c>
       <c r="H17" t="n">
-        <v>578.85</v>
+        <v>614.5</v>
       </c>
       <c r="I17" t="n">
         <v>596.4893806946769</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.59</v>
+        <v>-14.22</v>
       </c>
       <c r="L17" t="n">
-        <v>9.630000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="M17" t="n">
         <v>0.65</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>11.45</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45306</v>
+        <v>45307</v>
       </c>
       <c r="H18" t="n">
-        <v>599.5</v>
+        <v>589.65</v>
       </c>
       <c r="I18" t="n">
         <v>591.1399207513127</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.44</v>
+        <v>-4.04</v>
       </c>
       <c r="L18" t="n">
         <v>5.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="N18" t="n">
         <v>3.58</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.07</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H19" t="n">
-        <v>618.2</v>
+        <v>629.25</v>
       </c>
       <c r="I19" t="n">
         <v>627.2519314273552</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.84</v>
+        <v>-6.72</v>
       </c>
       <c r="L19" t="n">
-        <v>5.16</v>
+        <v>7.3</v>
       </c>
       <c r="M19" t="n">
         <v>3.28</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.76</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H20" t="n">
-        <v>625.35</v>
+        <v>608.25</v>
       </c>
       <c r="I20" t="n">
         <v>617.5704129387317</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.62</v>
+        <v>-3.34</v>
       </c>
       <c r="L20" t="n">
         <v>7.83</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>15.54</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H21" t="n">
-        <v>638.05</v>
+        <v>651.1</v>
       </c>
       <c r="I21" t="n">
         <v>639.5523871974767</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.9</v>
+        <v>-7.04</v>
       </c>
       <c r="L21" t="n">
-        <v>6.52</v>
+        <v>8.01</v>
       </c>
       <c r="M21" t="n">
         <v>3.46</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>12.48</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H22" t="n">
-        <v>689.2</v>
+        <v>658.35</v>
       </c>
       <c r="I22" t="n">
         <v>659.1736423445083</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K22" t="n">
-        <v>5.85</v>
+        <v>1.11</v>
       </c>
       <c r="L22" t="n">
         <v>7.08</v>
       </c>
       <c r="M22" t="n">
-        <v>1.14</v>
+        <v>2.64</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>4.48</v>
       </c>
       <c r="O22" t="n">
         <v>2.05</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>12.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H23" t="n">
-        <v>722.4</v>
+        <v>733.85</v>
       </c>
       <c r="I23" t="n">
         <v>728.4923948338529</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.73</v>
+        <v>-11.47</v>
       </c>
       <c r="L23" t="n">
-        <v>11.93</v>
+        <v>14.29</v>
       </c>
       <c r="M23" t="n">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="N23" t="n">
         <v>5.27</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.07</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45574</v>
+        <v>45575</v>
       </c>
       <c r="H24" t="n">
-        <v>673.1</v>
+        <v>670.8</v>
       </c>
       <c r="I24" t="n">
         <v>671.9353091241743</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.59</v>
       </c>
       <c r="L24" t="n">
         <v>9.48</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.85</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="H25" t="n">
-        <v>644.1</v>
+        <v>729.45</v>
       </c>
       <c r="I25" t="n">
         <v>690.945575175379</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>3.98</v>
+        <v>-8.74</v>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>11.05</v>
       </c>
       <c r="M25" t="n">
-        <v>0.89</v>
+        <v>3.09</v>
       </c>
       <c r="N25" t="n">
-        <v>1.38</v>
+        <v>13.25</v>
       </c>
       <c r="O25" t="n">
         <v>-0.34</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>14.93</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="H26" t="n">
-        <v>635.4</v>
+        <v>631.8</v>
       </c>
       <c r="I26" t="n">
         <v>635.1802974943075</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K26" t="n">
-        <v>-12.89</v>
+        <v>-13.39</v>
       </c>
       <c r="L26" t="n">
-        <v>13.36</v>
+        <v>14.17</v>
       </c>
       <c r="M26" t="n">
         <v>0.61</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.68</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H27" t="n">
-        <v>451.6</v>
+        <v>478.45</v>
       </c>
       <c r="I27" t="n">
         <v>463.7902749888139</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K27" t="n">
-        <v>28.52</v>
+        <v>24.27</v>
       </c>
       <c r="L27" t="n">
         <v>1.31</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>15.26</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="H28" t="n">
-        <v>500.2</v>
+        <v>479.95</v>
       </c>
       <c r="I28" t="n">
         <v>495.8220605762825</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>4.55</v>
+        <v>0.31</v>
       </c>
       <c r="L28" t="n">
         <v>5.74</v>
@@ -2037,7 +2372,7 @@
         <v>8.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="O28" t="n">
         <v>5.95</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45856</v>
+        <v>45859</v>
       </c>
       <c r="H29" t="n">
-        <v>479.75</v>
+        <v>487.9</v>
       </c>
       <c r="I29" t="n">
         <v>486.5770113488817</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>0.04</v>
+        <v>-1.66</v>
       </c>
       <c r="L29" t="n">
         <v>5</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H30" t="n">
-        <v>449.55</v>
+        <v>437.55</v>
       </c>
       <c r="I30" t="n">
         <v>444.549787986739</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.86</v>
+        <v>-10.32</v>
       </c>
       <c r="L30" t="n">
-        <v>8.789999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="M30" t="n">
         <v>2.88</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.57</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="H31" t="n">
-        <v>435.75</v>
+        <v>452.8</v>
       </c>
       <c r="I31" t="n">
         <v>440.4281950392094</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K31" t="n">
-        <v>0.41</v>
+        <v>-3.49</v>
       </c>
       <c r="L31" t="n">
         <v>6.65</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.7</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H32" t="n">
-        <v>479.15</v>
+        <v>471.55</v>
       </c>
       <c r="I32" t="n">
         <v>475.8623079903146</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K32" t="n">
-        <v>5.82</v>
+        <v>4.14</v>
       </c>
       <c r="L32" t="n">
         <v>4.06</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.43</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="H33" t="n">
-        <v>456.1</v>
+        <v>487.8</v>
       </c>
       <c r="I33" t="n">
         <v>475.4763281348324</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K33" t="n">
-        <v>3.28</v>
+        <v>-3.45</v>
       </c>
       <c r="L33" t="n">
         <v>6.52</v>
       </c>
       <c r="M33" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>5.55</v>
+        <v>6.95</v>
       </c>
       <c r="O33" t="n">
         <v>-1.59</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.13</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H34" t="n">
-        <v>510.3</v>
+        <v>486.05</v>
       </c>
       <c r="I34" t="n">
         <v>500.3322855115686</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K34" t="n">
-        <v>4.61</v>
+        <v>-0.36</v>
       </c>
       <c r="L34" t="n">
         <v>5.45</v>
@@ -2379,7 +2786,7 @@
         <v>6.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.23</v>
+        <v>4.75</v>
       </c>
       <c r="O34" t="n">
         <v>6.95</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.44</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H35" t="n">
-        <v>523.05</v>
+        <v>554.25</v>
       </c>
       <c r="I35" t="n">
         <v>537.5892559042686</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.61</v>
+        <v>-14.03</v>
       </c>
       <c r="L35" t="n">
-        <v>11.81</v>
+        <v>15.18</v>
       </c>
       <c r="M35" t="n">
         <v>2.88</v>
       </c>
       <c r="N35" t="n">
-        <v>3.6</v>
+        <v>5.97</v>
       </c>
       <c r="O35" t="n">
         <v>-4.75</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.17</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H36" t="n">
-        <v>794</v>
+        <v>765.9</v>
       </c>
       <c r="I36" t="n">
         <v>767.7256461098668</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K36" t="n">
-        <v>43.26</v>
+        <v>38.19</v>
       </c>
       <c r="L36" t="n">
         <v>5.07</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>11.19</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H37" t="n">
-        <v>781.9</v>
+        <v>851.85</v>
       </c>
       <c r="I37" t="n">
         <v>833.0974992245117</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.09</v>
+        <v>-11.22</v>
       </c>
       <c r="L37" t="n">
-        <v>4.62</v>
+        <v>13.33</v>
       </c>
       <c r="M37" t="n">
-        <v>0.48</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>3.86</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O37" t="n">
         <v>-3.54</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2610,6 +3065,12 @@
       <c r="Q38" t="n">
         <v>2</v>
       </c>
+      <c r="R38" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4950,7 +5411,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -4960,7 +5421,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -4970,7 +5431,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -4980,7 +5441,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -4990,7 +5451,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57.8</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="10">
@@ -5000,7 +5461,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104.5</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="11">
@@ -5010,7 +5471,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -5020,7 +5481,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -5030,7 +5491,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
@@ -5040,7 +5501,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.93</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="15">
@@ -5050,7 +5511,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.66</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="16">
@@ -5060,7 +5521,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.21</v>
+        <v>-4.53</v>
       </c>
     </row>
     <row r="17">
@@ -5070,7 +5531,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73.34</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="18">
@@ -5080,7 +5541,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -5090,7 +5551,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.11</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="20">
@@ -5100,7 +5561,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.13</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="21">
@@ -5110,7 +5571,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.59</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="22">
@@ -5120,7 +5581,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -5130,7 +5591,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -5140,7 +5601,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -5160,7 +5621,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.81</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="27">
@@ -5170,7 +5631,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.07</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="28">
@@ -5180,7 +5641,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
